--- a/templates/PI Template.xlsx
+++ b/templates/PI Template.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\ys-project\auto-contact-desktop\templates\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\ys-project\Auto-Contract\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{74A36B30-D0D0-45DA-85A9-3BDEF7B264DD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AC8E1932-0763-425D-B83B-1455CC9B61E1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{A576A92E-B579-48C0-ABED-659401E18BC8}"/>
   </bookViews>
@@ -64,10 +64,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>Sleer Informatuon/卖方信息</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>1.TERMS OF PAYMENT / 支付条款</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -172,19 +168,7 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>{{unit_price}}</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>{{total_amount}}</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>Total Amount：${{total_amount}} (in words: {{total_amount_words_en}})</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>合计金额：{{total_amount}}美元（大写：{{total_amount_words_cn}}）</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -255,6 +239,22 @@
   </si>
   <si>
     <t>EMAIL: {{seller_email}}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>${{total_amount}}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>${{unit_price}}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>合计金额：${{total_amount}}美元（大写：{{total_amount_words_cn}}）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Seller Information/卖方信息</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -613,119 +613,119 @@
     <xf numFmtId="177" fontId="7" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="178" fontId="7" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="8" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="10" fontId="8" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="176" fontId="8" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="4" fontId="8" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="justify" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="4" fontId="8" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="176" fontId="8" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="8" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="10" fontId="8" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="178" fontId="7" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1132,53 +1132,53 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="24.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="50" t="s">
+      <c r="A1" s="28" t="s">
         <v>3</v>
       </c>
-      <c r="B1" s="51"/>
-      <c r="C1" s="51"/>
-      <c r="D1" s="51"/>
-      <c r="E1" s="51"/>
-      <c r="F1" s="51"/>
-      <c r="G1" s="51"/>
-      <c r="H1" s="51"/>
-      <c r="I1" s="51"/>
-      <c r="J1" s="51"/>
+      <c r="B1" s="29"/>
+      <c r="C1" s="29"/>
+      <c r="D1" s="29"/>
+      <c r="E1" s="29"/>
+      <c r="F1" s="29"/>
+      <c r="G1" s="29"/>
+      <c r="H1" s="29"/>
+      <c r="I1" s="29"/>
+      <c r="J1" s="29"/>
     </row>
     <row r="2" spans="1:10" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="51"/>
-      <c r="B2" s="51"/>
-      <c r="C2" s="51"/>
-      <c r="D2" s="51"/>
-      <c r="E2" s="51"/>
-      <c r="F2" s="51"/>
-      <c r="G2" s="51"/>
-      <c r="H2" s="51"/>
-      <c r="I2" s="51"/>
-      <c r="J2" s="51"/>
+      <c r="A2" s="29"/>
+      <c r="B2" s="29"/>
+      <c r="C2" s="29"/>
+      <c r="D2" s="29"/>
+      <c r="E2" s="29"/>
+      <c r="F2" s="29"/>
+      <c r="G2" s="29"/>
+      <c r="H2" s="29"/>
+      <c r="I2" s="29"/>
+      <c r="J2" s="29"/>
     </row>
     <row r="3" spans="1:10" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="52" t="s">
+      <c r="A3" s="30" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="53"/>
-      <c r="C3" s="53"/>
-      <c r="D3" s="53"/>
-      <c r="E3" s="53"/>
-      <c r="F3" s="53"/>
-      <c r="G3" s="53"/>
-      <c r="H3" s="53"/>
-      <c r="I3" s="53"/>
-      <c r="J3" s="53"/>
+      <c r="B3" s="31"/>
+      <c r="C3" s="31"/>
+      <c r="D3" s="31"/>
+      <c r="E3" s="31"/>
+      <c r="F3" s="31"/>
+      <c r="G3" s="31"/>
+      <c r="H3" s="31"/>
+      <c r="I3" s="31"/>
+      <c r="J3" s="31"/>
     </row>
     <row r="4" spans="1:10" customFormat="1" ht="28.5" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="5" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="30" t="s">
+      <c r="A5" s="37" t="s">
         <v>5</v>
       </c>
-      <c r="B5" s="30"/>
-      <c r="C5" s="30"/>
-      <c r="D5" s="30"/>
+      <c r="B5" s="37"/>
+      <c r="C5" s="37"/>
+      <c r="D5" s="37"/>
       <c r="E5" s="6"/>
       <c r="F5" s="6"/>
       <c r="G5" s="7"/>
@@ -1187,105 +1187,105 @@
       <c r="J5" s="7"/>
     </row>
     <row r="6" spans="1:10" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="59" t="s">
+      <c r="A6" s="38" t="s">
+        <v>17</v>
+      </c>
+      <c r="B6" s="38"/>
+      <c r="C6" s="38"/>
+      <c r="D6" s="38"/>
+      <c r="E6" s="38"/>
+      <c r="F6" s="38"/>
+      <c r="G6" s="21" t="s">
+        <v>10</v>
+      </c>
+      <c r="H6" s="35" t="s">
+        <v>16</v>
+      </c>
+      <c r="I6" s="35"/>
+      <c r="J6" s="35"/>
+    </row>
+    <row r="7" spans="1:10" ht="42.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A7" s="52" t="s">
+        <v>43</v>
+      </c>
+      <c r="B7" s="53"/>
+      <c r="C7" s="53"/>
+      <c r="D7" s="53"/>
+      <c r="E7" s="53"/>
+      <c r="F7" s="54"/>
+      <c r="G7" s="22" t="s">
+        <v>14</v>
+      </c>
+      <c r="H7" s="36" t="s">
+        <v>33</v>
+      </c>
+      <c r="I7" s="36"/>
+      <c r="J7" s="36"/>
+    </row>
+    <row r="8" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A8" s="52" t="s">
+        <v>44</v>
+      </c>
+      <c r="B8" s="53"/>
+      <c r="C8" s="53"/>
+      <c r="D8" s="53"/>
+      <c r="E8" s="53"/>
+      <c r="F8" s="54"/>
+      <c r="G8" s="23" t="s">
+        <v>11</v>
+      </c>
+      <c r="H8" s="39" t="s">
         <v>18</v>
       </c>
-      <c r="B6" s="59"/>
-      <c r="C6" s="59"/>
-      <c r="D6" s="59"/>
-      <c r="E6" s="59"/>
-      <c r="F6" s="59"/>
-      <c r="G6" s="21" t="s">
-        <v>11</v>
-      </c>
-      <c r="H6" s="57" t="s">
-        <v>17</v>
-      </c>
-      <c r="I6" s="57"/>
-      <c r="J6" s="57"/>
-    </row>
-    <row r="7" spans="1:10" ht="42.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="34" t="s">
-        <v>47</v>
-      </c>
-      <c r="B7" s="35"/>
-      <c r="C7" s="35"/>
-      <c r="D7" s="35"/>
-      <c r="E7" s="35"/>
-      <c r="F7" s="36"/>
-      <c r="G7" s="22" t="s">
-        <v>15</v>
-      </c>
-      <c r="H7" s="58" t="s">
-        <v>37</v>
-      </c>
-      <c r="I7" s="58"/>
-      <c r="J7" s="58"/>
-    </row>
-    <row r="8" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="34" t="s">
-        <v>48</v>
-      </c>
-      <c r="B8" s="35"/>
-      <c r="C8" s="35"/>
-      <c r="D8" s="35"/>
-      <c r="E8" s="35"/>
-      <c r="F8" s="36"/>
-      <c r="G8" s="23" t="s">
+      <c r="I8" s="40"/>
+      <c r="J8" s="41"/>
+    </row>
+    <row r="9" spans="1:10" ht="18.95" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A9" s="52"/>
+      <c r="B9" s="53"/>
+      <c r="C9" s="53"/>
+      <c r="D9" s="53"/>
+      <c r="E9" s="53"/>
+      <c r="F9" s="54"/>
+      <c r="G9" s="24" t="s">
         <v>12</v>
       </c>
-      <c r="H8" s="60" t="s">
+      <c r="H9" s="42" t="s">
         <v>19</v>
       </c>
-      <c r="I8" s="61"/>
-      <c r="J8" s="62"/>
-    </row>
-    <row r="9" spans="1:10" ht="18.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="34"/>
-      <c r="B9" s="35"/>
-      <c r="C9" s="35"/>
-      <c r="D9" s="35"/>
-      <c r="E9" s="35"/>
-      <c r="F9" s="36"/>
-      <c r="G9" s="24" t="s">
+      <c r="I9" s="43"/>
+      <c r="J9" s="44"/>
+    </row>
+    <row r="10" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A10" s="55" t="s">
+        <v>45</v>
+      </c>
+      <c r="B10" s="56"/>
+      <c r="C10" s="56"/>
+      <c r="D10" s="56"/>
+      <c r="E10" s="56"/>
+      <c r="F10" s="57"/>
+      <c r="G10" s="33" t="s">
         <v>13</v>
       </c>
-      <c r="H9" s="63" t="s">
-        <v>20</v>
-      </c>
-      <c r="I9" s="64"/>
-      <c r="J9" s="65"/>
-    </row>
-    <row r="10" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="37" t="s">
-        <v>49</v>
-      </c>
-      <c r="B10" s="38"/>
-      <c r="C10" s="38"/>
-      <c r="D10" s="38"/>
-      <c r="E10" s="38"/>
-      <c r="F10" s="39"/>
-      <c r="G10" s="55" t="s">
-        <v>14</v>
-      </c>
-      <c r="H10" s="55"/>
-      <c r="I10" s="55"/>
-      <c r="J10" s="56"/>
+      <c r="H10" s="33"/>
+      <c r="I10" s="33"/>
+      <c r="J10" s="34"/>
     </row>
     <row r="11" spans="1:10" ht="18.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="37"/>
-      <c r="B11" s="38"/>
-      <c r="C11" s="38"/>
-      <c r="D11" s="38"/>
-      <c r="E11" s="38"/>
-      <c r="F11" s="39"/>
+      <c r="A11" s="55"/>
+      <c r="B11" s="56"/>
+      <c r="C11" s="56"/>
+      <c r="D11" s="56"/>
+      <c r="E11" s="56"/>
+      <c r="F11" s="57"/>
       <c r="G11" s="25" t="s">
         <v>0</v>
       </c>
       <c r="H11" s="8"/>
       <c r="I11" s="8"/>
       <c r="J11" s="26" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
     </row>
     <row r="12" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.2">
@@ -1295,114 +1295,114 @@
       <c r="D12" s="19"/>
       <c r="E12" s="19"/>
       <c r="F12" s="20"/>
-      <c r="G12" s="54" t="s">
+      <c r="G12" s="32" t="s">
         <v>1</v>
       </c>
-      <c r="H12" s="54"/>
-      <c r="I12" s="54"/>
+      <c r="H12" s="32"/>
+      <c r="I12" s="32"/>
       <c r="J12" s="27" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
     </row>
     <row r="13" spans="1:10" ht="33.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="B13" s="60" t="s">
+        <v>36</v>
+      </c>
+      <c r="C13" s="60"/>
+      <c r="D13" s="60"/>
+      <c r="E13" s="9" t="s">
+        <v>38</v>
+      </c>
+      <c r="F13" s="9" t="s">
+        <v>39</v>
+      </c>
+      <c r="G13" s="10" t="s">
+        <v>40</v>
+      </c>
+      <c r="H13" s="10" t="s">
         <v>41</v>
       </c>
-      <c r="B13" s="44" t="s">
-        <v>40</v>
-      </c>
-      <c r="C13" s="44"/>
-      <c r="D13" s="44"/>
-      <c r="E13" s="9" t="s">
+      <c r="I13" s="61" t="s">
         <v>42</v>
       </c>
-      <c r="F13" s="9" t="s">
-        <v>43</v>
-      </c>
-      <c r="G13" s="10" t="s">
-        <v>44</v>
-      </c>
-      <c r="H13" s="10" t="s">
-        <v>45</v>
-      </c>
-      <c r="I13" s="45" t="s">
-        <v>46</v>
-      </c>
-      <c r="J13" s="45"/>
+      <c r="J13" s="61"/>
     </row>
     <row r="14" spans="1:10" ht="31.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="40">
+      <c r="A14" s="45">
         <v>1</v>
       </c>
-      <c r="B14" s="40" t="s">
+      <c r="B14" s="45" t="s">
+        <v>27</v>
+      </c>
+      <c r="C14" s="45"/>
+      <c r="D14" s="45"/>
+      <c r="E14" s="46" t="s">
+        <v>29</v>
+      </c>
+      <c r="F14" s="47" t="s">
+        <v>30</v>
+      </c>
+      <c r="G14" s="45" t="s">
+        <v>31</v>
+      </c>
+      <c r="H14" s="58" t="s">
+        <v>50</v>
+      </c>
+      <c r="I14" s="48" t="s">
+        <v>49</v>
+      </c>
+      <c r="J14" s="48"/>
+    </row>
+    <row r="15" spans="1:10" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A15" s="45"/>
+      <c r="B15" s="45" t="s">
         <v>28</v>
       </c>
-      <c r="C14" s="40"/>
-      <c r="D14" s="40"/>
-      <c r="E14" s="47" t="s">
-        <v>30</v>
-      </c>
-      <c r="F14" s="48" t="s">
-        <v>31</v>
-      </c>
-      <c r="G14" s="40" t="s">
+      <c r="C15" s="45"/>
+      <c r="D15" s="45"/>
+      <c r="E15" s="46"/>
+      <c r="F15" s="47"/>
+      <c r="G15" s="45"/>
+      <c r="H15" s="58"/>
+      <c r="I15" s="48"/>
+      <c r="J15" s="48"/>
+    </row>
+    <row r="16" spans="1:10" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A16" s="59" t="s">
         <v>32</v>
       </c>
-      <c r="H14" s="41" t="s">
-        <v>33</v>
-      </c>
-      <c r="I14" s="42" t="s">
-        <v>34</v>
-      </c>
-      <c r="J14" s="42"/>
-    </row>
-    <row r="15" spans="1:10" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A15" s="40"/>
-      <c r="B15" s="40" t="s">
-        <v>29</v>
-      </c>
-      <c r="C15" s="40"/>
-      <c r="D15" s="40"/>
-      <c r="E15" s="47"/>
-      <c r="F15" s="48"/>
-      <c r="G15" s="40"/>
-      <c r="H15" s="41"/>
-      <c r="I15" s="42"/>
-      <c r="J15" s="42"/>
-    </row>
-    <row r="16" spans="1:10" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="43" t="s">
-        <v>35</v>
-      </c>
-      <c r="B16" s="43"/>
-      <c r="C16" s="43"/>
-      <c r="D16" s="43"/>
-      <c r="E16" s="43"/>
-      <c r="F16" s="43"/>
-      <c r="G16" s="43"/>
-      <c r="H16" s="43"/>
-      <c r="I16" s="42" t="s">
-        <v>34</v>
-      </c>
-      <c r="J16" s="42"/>
+      <c r="B16" s="59"/>
+      <c r="C16" s="59"/>
+      <c r="D16" s="59"/>
+      <c r="E16" s="59"/>
+      <c r="F16" s="59"/>
+      <c r="G16" s="59"/>
+      <c r="H16" s="59"/>
+      <c r="I16" s="48" t="s">
+        <v>49</v>
+      </c>
+      <c r="J16" s="48"/>
     </row>
     <row r="17" spans="1:23" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="43" t="s">
-        <v>36</v>
-      </c>
-      <c r="B17" s="43"/>
-      <c r="C17" s="43"/>
-      <c r="D17" s="43"/>
-      <c r="E17" s="43"/>
-      <c r="F17" s="43"/>
-      <c r="G17" s="43"/>
-      <c r="H17" s="43"/>
-      <c r="I17" s="42"/>
-      <c r="J17" s="42"/>
+      <c r="A17" s="59" t="s">
+        <v>51</v>
+      </c>
+      <c r="B17" s="59"/>
+      <c r="C17" s="59"/>
+      <c r="D17" s="59"/>
+      <c r="E17" s="59"/>
+      <c r="F17" s="59"/>
+      <c r="G17" s="59"/>
+      <c r="H17" s="59"/>
+      <c r="I17" s="48"/>
+      <c r="J17" s="48"/>
     </row>
     <row r="18" spans="1:23" ht="27.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="49" t="s">
-        <v>6</v>
+        <v>52</v>
       </c>
       <c r="B18" s="49"/>
       <c r="C18" s="49"/>
@@ -1415,27 +1415,27 @@
       <c r="J18" s="49"/>
     </row>
     <row r="19" spans="1:23" ht="18.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A19" s="31" t="s">
+      <c r="A19" s="51" t="s">
+        <v>25</v>
+      </c>
+      <c r="B19" s="51"/>
+      <c r="C19" s="51"/>
+      <c r="D19" s="51"/>
+      <c r="E19" s="51"/>
+      <c r="F19" s="7"/>
+      <c r="G19" s="62"/>
+      <c r="H19" s="62"/>
+      <c r="I19" s="62"/>
+      <c r="J19" s="62"/>
+    </row>
+    <row r="20" spans="1:23" ht="18.95" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A20" s="51" t="s">
         <v>26</v>
       </c>
-      <c r="B19" s="31"/>
-      <c r="C19" s="31"/>
-      <c r="D19" s="31"/>
-      <c r="E19" s="31"/>
-      <c r="F19" s="7"/>
-      <c r="G19" s="46"/>
-      <c r="H19" s="46"/>
-      <c r="I19" s="46"/>
-      <c r="J19" s="46"/>
-    </row>
-    <row r="20" spans="1:23" ht="18.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A20" s="31" t="s">
-        <v>27</v>
-      </c>
-      <c r="B20" s="31"/>
-      <c r="C20" s="31"/>
-      <c r="D20" s="31"/>
-      <c r="E20" s="31"/>
+      <c r="B20" s="51"/>
+      <c r="C20" s="51"/>
+      <c r="D20" s="51"/>
+      <c r="E20" s="51"/>
       <c r="F20" s="7"/>
       <c r="G20" s="11"/>
       <c r="H20" s="11"/>
@@ -1443,54 +1443,54 @@
       <c r="J20" s="11"/>
     </row>
     <row r="21" spans="1:23" ht="18.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A21" s="31" t="s">
-        <v>50</v>
-      </c>
-      <c r="B21" s="31"/>
-      <c r="C21" s="31"/>
-      <c r="D21" s="31"/>
-      <c r="E21" s="31"/>
-      <c r="F21" s="31"/>
-      <c r="G21" s="31"/>
-      <c r="H21" s="31"/>
-      <c r="I21" s="31"/>
+      <c r="A21" s="51" t="s">
+        <v>46</v>
+      </c>
+      <c r="B21" s="51"/>
+      <c r="C21" s="51"/>
+      <c r="D21" s="51"/>
+      <c r="E21" s="51"/>
+      <c r="F21" s="51"/>
+      <c r="G21" s="51"/>
+      <c r="H21" s="51"/>
+      <c r="I21" s="51"/>
       <c r="J21" s="11"/>
     </row>
     <row r="22" spans="1:23" ht="18.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A22" s="31" t="s">
-        <v>51</v>
-      </c>
-      <c r="B22" s="31"/>
-      <c r="C22" s="31"/>
-      <c r="D22" s="31"/>
-      <c r="E22" s="31"/>
-      <c r="F22" s="31"/>
-      <c r="G22" s="31"/>
-      <c r="H22" s="31"/>
-      <c r="I22" s="31"/>
+      <c r="A22" s="51" t="s">
+        <v>47</v>
+      </c>
+      <c r="B22" s="51"/>
+      <c r="C22" s="51"/>
+      <c r="D22" s="51"/>
+      <c r="E22" s="51"/>
+      <c r="F22" s="51"/>
+      <c r="G22" s="51"/>
+      <c r="H22" s="51"/>
+      <c r="I22" s="51"/>
       <c r="J22" s="11"/>
     </row>
     <row r="23" spans="1:23" ht="18.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A23" s="31" t="s">
-        <v>52</v>
-      </c>
-      <c r="B23" s="31"/>
-      <c r="C23" s="31"/>
-      <c r="D23" s="31"/>
-      <c r="E23" s="31"/>
-      <c r="F23" s="31"/>
-      <c r="G23" s="31"/>
-      <c r="H23" s="31"/>
-      <c r="I23" s="31"/>
+      <c r="A23" s="51" t="s">
+        <v>48</v>
+      </c>
+      <c r="B23" s="51"/>
+      <c r="C23" s="51"/>
+      <c r="D23" s="51"/>
+      <c r="E23" s="51"/>
+      <c r="F23" s="51"/>
+      <c r="G23" s="51"/>
+      <c r="H23" s="51"/>
+      <c r="I23" s="51"/>
       <c r="J23" s="11"/>
     </row>
     <row r="24" spans="1:23" ht="27.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A24" s="30" t="s">
-        <v>7</v>
-      </c>
-      <c r="B24" s="30"/>
-      <c r="C24" s="30"/>
-      <c r="D24" s="30"/>
+      <c r="A24" s="37" t="s">
+        <v>6</v>
+      </c>
+      <c r="B24" s="37"/>
+      <c r="C24" s="37"/>
+      <c r="D24" s="37"/>
       <c r="E24" s="12"/>
       <c r="F24" s="12"/>
       <c r="G24" s="12"/>
@@ -1499,18 +1499,18 @@
       <c r="J24" s="13"/>
     </row>
     <row r="25" spans="1:23" ht="33" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A25" s="32" t="s">
-        <v>21</v>
-      </c>
-      <c r="B25" s="32"/>
-      <c r="C25" s="32"/>
-      <c r="D25" s="32"/>
-      <c r="E25" s="32"/>
-      <c r="F25" s="32"/>
-      <c r="G25" s="32"/>
-      <c r="H25" s="32"/>
-      <c r="I25" s="32"/>
-      <c r="J25" s="32"/>
+      <c r="A25" s="50" t="s">
+        <v>20</v>
+      </c>
+      <c r="B25" s="50"/>
+      <c r="C25" s="50"/>
+      <c r="D25" s="50"/>
+      <c r="E25" s="50"/>
+      <c r="F25" s="50"/>
+      <c r="G25" s="50"/>
+      <c r="H25" s="50"/>
+      <c r="I25" s="50"/>
+      <c r="J25" s="50"/>
       <c r="K25" s="2"/>
       <c r="L25" s="2"/>
       <c r="M25" s="2"/>
@@ -1526,16 +1526,16 @@
       <c r="W25" s="2"/>
     </row>
     <row r="26" spans="1:23" ht="36.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A26" s="32"/>
-      <c r="B26" s="32"/>
-      <c r="C26" s="32"/>
-      <c r="D26" s="32"/>
-      <c r="E26" s="32"/>
-      <c r="F26" s="32"/>
-      <c r="G26" s="32"/>
-      <c r="H26" s="32"/>
-      <c r="I26" s="32"/>
-      <c r="J26" s="32"/>
+      <c r="A26" s="50"/>
+      <c r="B26" s="50"/>
+      <c r="C26" s="50"/>
+      <c r="D26" s="50"/>
+      <c r="E26" s="50"/>
+      <c r="F26" s="50"/>
+      <c r="G26" s="50"/>
+      <c r="H26" s="50"/>
+      <c r="I26" s="50"/>
+      <c r="J26" s="50"/>
       <c r="K26" s="2"/>
       <c r="L26" s="2"/>
       <c r="M26" s="2"/>
@@ -1551,112 +1551,112 @@
       <c r="W26" s="2"/>
     </row>
     <row r="27" spans="1:23" ht="36.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A27" s="32" t="s">
-        <v>22</v>
-      </c>
-      <c r="B27" s="32"/>
-      <c r="C27" s="32"/>
-      <c r="D27" s="32"/>
-      <c r="E27" s="32"/>
-      <c r="F27" s="32"/>
-      <c r="G27" s="32"/>
-      <c r="H27" s="32"/>
-      <c r="I27" s="32"/>
-      <c r="J27" s="32"/>
+      <c r="A27" s="50" t="s">
+        <v>21</v>
+      </c>
+      <c r="B27" s="50"/>
+      <c r="C27" s="50"/>
+      <c r="D27" s="50"/>
+      <c r="E27" s="50"/>
+      <c r="F27" s="50"/>
+      <c r="G27" s="50"/>
+      <c r="H27" s="50"/>
+      <c r="I27" s="50"/>
+      <c r="J27" s="50"/>
     </row>
     <row r="28" spans="1:23" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A28" s="32"/>
-      <c r="B28" s="32"/>
-      <c r="C28" s="32"/>
-      <c r="D28" s="32"/>
-      <c r="E28" s="32"/>
-      <c r="F28" s="32"/>
-      <c r="G28" s="32"/>
-      <c r="H28" s="32"/>
-      <c r="I28" s="32"/>
-      <c r="J28" s="32"/>
+      <c r="A28" s="50"/>
+      <c r="B28" s="50"/>
+      <c r="C28" s="50"/>
+      <c r="D28" s="50"/>
+      <c r="E28" s="50"/>
+      <c r="F28" s="50"/>
+      <c r="G28" s="50"/>
+      <c r="H28" s="50"/>
+      <c r="I28" s="50"/>
+      <c r="J28" s="50"/>
     </row>
     <row r="29" spans="1:23" ht="27.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A29" s="30" t="s">
-        <v>8</v>
-      </c>
-      <c r="B29" s="30"/>
-      <c r="C29" s="30"/>
-      <c r="D29" s="30"/>
-      <c r="E29" s="30"/>
-      <c r="F29" s="30"/>
-      <c r="G29" s="30"/>
+      <c r="A29" s="37" t="s">
+        <v>7</v>
+      </c>
+      <c r="B29" s="37"/>
+      <c r="C29" s="37"/>
+      <c r="D29" s="37"/>
+      <c r="E29" s="37"/>
+      <c r="F29" s="37"/>
+      <c r="G29" s="37"/>
       <c r="H29" s="14"/>
       <c r="I29" s="14"/>
       <c r="J29" s="14"/>
       <c r="K29" s="3"/>
     </row>
     <row r="30" spans="1:23" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A30" s="32" t="s">
-        <v>23</v>
-      </c>
-      <c r="B30" s="32"/>
-      <c r="C30" s="32"/>
-      <c r="D30" s="32"/>
-      <c r="E30" s="32"/>
-      <c r="F30" s="32"/>
-      <c r="G30" s="32"/>
+      <c r="A30" s="50" t="s">
+        <v>22</v>
+      </c>
+      <c r="B30" s="50"/>
+      <c r="C30" s="50"/>
+      <c r="D30" s="50"/>
+      <c r="E30" s="50"/>
+      <c r="F30" s="50"/>
+      <c r="G30" s="50"/>
       <c r="H30" s="15"/>
       <c r="I30" s="15"/>
       <c r="J30" s="15"/>
       <c r="K30" s="3"/>
     </row>
     <row r="31" spans="1:23" ht="27.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A31" s="30" t="s">
+      <c r="A31" s="37" t="s">
         <v>2</v>
       </c>
-      <c r="B31" s="30"/>
-      <c r="C31" s="30"/>
-      <c r="D31" s="30"/>
-      <c r="E31" s="30"/>
-      <c r="F31" s="30"/>
-      <c r="G31" s="30"/>
+      <c r="B31" s="37"/>
+      <c r="C31" s="37"/>
+      <c r="D31" s="37"/>
+      <c r="E31" s="37"/>
+      <c r="F31" s="37"/>
+      <c r="G31" s="37"/>
       <c r="H31" s="7"/>
       <c r="I31" s="7"/>
       <c r="J31" s="7"/>
       <c r="K31" s="4"/>
     </row>
     <row r="32" spans="1:23" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A32" s="33" t="s">
-        <v>24</v>
-      </c>
-      <c r="B32" s="33"/>
-      <c r="C32" s="33"/>
-      <c r="D32" s="33"/>
-      <c r="E32" s="33"/>
-      <c r="F32" s="33"/>
-      <c r="G32" s="33"/>
+      <c r="A32" s="65" t="s">
+        <v>23</v>
+      </c>
+      <c r="B32" s="65"/>
+      <c r="C32" s="65"/>
+      <c r="D32" s="65"/>
+      <c r="E32" s="65"/>
+      <c r="F32" s="65"/>
+      <c r="G32" s="65"/>
       <c r="H32" s="16"/>
       <c r="I32" s="16"/>
       <c r="J32" s="16"/>
       <c r="K32" s="4"/>
     </row>
     <row r="33" spans="1:11" ht="27.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A33" s="29" t="s">
-        <v>9</v>
-      </c>
-      <c r="B33" s="29"/>
-      <c r="C33" s="29"/>
-      <c r="D33" s="29"/>
-      <c r="E33" s="29"/>
-      <c r="F33" s="29"/>
-      <c r="G33" s="29"/>
+      <c r="A33" s="64" t="s">
+        <v>8</v>
+      </c>
+      <c r="B33" s="64"/>
+      <c r="C33" s="64"/>
+      <c r="D33" s="64"/>
+      <c r="E33" s="64"/>
+      <c r="F33" s="64"/>
+      <c r="G33" s="64"/>
       <c r="H33" s="7"/>
       <c r="I33" s="7"/>
       <c r="J33" s="7"/>
       <c r="K33" s="5"/>
     </row>
     <row r="34" spans="1:11" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A34" s="31" t="s">
-        <v>10</v>
-      </c>
-      <c r="B34" s="31"/>
-      <c r="C34" s="31"/>
+      <c r="A34" s="51" t="s">
+        <v>9</v>
+      </c>
+      <c r="B34" s="51"/>
+      <c r="C34" s="51"/>
       <c r="D34" s="7"/>
       <c r="E34" s="7"/>
       <c r="F34" s="7"/>
@@ -1666,55 +1666,43 @@
       <c r="J34" s="7"/>
     </row>
     <row r="35" spans="1:11" ht="27.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A35" s="29" t="s">
-        <v>16</v>
-      </c>
-      <c r="B35" s="29"/>
-      <c r="C35" s="29"/>
-      <c r="D35" s="29"/>
-      <c r="E35" s="29"/>
-      <c r="F35" s="29"/>
-      <c r="G35" s="29"/>
+      <c r="A35" s="64" t="s">
+        <v>15</v>
+      </c>
+      <c r="B35" s="64"/>
+      <c r="C35" s="64"/>
+      <c r="D35" s="64"/>
+      <c r="E35" s="64"/>
+      <c r="F35" s="64"/>
+      <c r="G35" s="64"/>
       <c r="H35" s="17"/>
       <c r="I35" s="17"/>
       <c r="J35" s="17"/>
     </row>
     <row r="36" spans="1:11" ht="138" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A36" s="28" t="s">
-        <v>25</v>
-      </c>
-      <c r="B36" s="28"/>
-      <c r="C36" s="28"/>
-      <c r="D36" s="28"/>
-      <c r="E36" s="28"/>
-      <c r="F36" s="28"/>
-      <c r="G36" s="28"/>
-      <c r="H36" s="28"/>
-      <c r="I36" s="28"/>
+      <c r="A36" s="63" t="s">
+        <v>24</v>
+      </c>
+      <c r="B36" s="63"/>
+      <c r="C36" s="63"/>
+      <c r="D36" s="63"/>
+      <c r="E36" s="63"/>
+      <c r="F36" s="63"/>
+      <c r="G36" s="63"/>
+      <c r="H36" s="63"/>
+      <c r="I36" s="63"/>
       <c r="J36" s="17"/>
     </row>
   </sheetData>
   <mergeCells count="44">
-    <mergeCell ref="A1:J2"/>
-    <mergeCell ref="A3:J3"/>
-    <mergeCell ref="G12:I12"/>
-    <mergeCell ref="G10:J10"/>
-    <mergeCell ref="H6:J6"/>
-    <mergeCell ref="H7:J7"/>
-    <mergeCell ref="A5:D5"/>
-    <mergeCell ref="A6:F6"/>
-    <mergeCell ref="H8:J8"/>
-    <mergeCell ref="H9:J9"/>
-    <mergeCell ref="A14:A15"/>
-    <mergeCell ref="E14:E15"/>
-    <mergeCell ref="F14:F15"/>
-    <mergeCell ref="I16:J17"/>
-    <mergeCell ref="A18:J18"/>
-    <mergeCell ref="A25:J26"/>
-    <mergeCell ref="A27:J28"/>
-    <mergeCell ref="A22:I22"/>
-    <mergeCell ref="A23:I23"/>
-    <mergeCell ref="A24:D24"/>
+    <mergeCell ref="A36:I36"/>
+    <mergeCell ref="A35:G35"/>
+    <mergeCell ref="A29:G29"/>
+    <mergeCell ref="A31:G31"/>
+    <mergeCell ref="A33:G33"/>
+    <mergeCell ref="A34:C34"/>
+    <mergeCell ref="A30:G30"/>
+    <mergeCell ref="A32:G32"/>
     <mergeCell ref="A20:E20"/>
     <mergeCell ref="A21:I21"/>
     <mergeCell ref="A7:F7"/>
@@ -1731,14 +1719,26 @@
     <mergeCell ref="B15:D15"/>
     <mergeCell ref="A19:E19"/>
     <mergeCell ref="G19:J19"/>
-    <mergeCell ref="A36:I36"/>
-    <mergeCell ref="A35:G35"/>
-    <mergeCell ref="A29:G29"/>
-    <mergeCell ref="A31:G31"/>
-    <mergeCell ref="A33:G33"/>
-    <mergeCell ref="A34:C34"/>
-    <mergeCell ref="A30:G30"/>
-    <mergeCell ref="A32:G32"/>
+    <mergeCell ref="A25:J26"/>
+    <mergeCell ref="A27:J28"/>
+    <mergeCell ref="A22:I22"/>
+    <mergeCell ref="A23:I23"/>
+    <mergeCell ref="A24:D24"/>
+    <mergeCell ref="A14:A15"/>
+    <mergeCell ref="E14:E15"/>
+    <mergeCell ref="F14:F15"/>
+    <mergeCell ref="I16:J17"/>
+    <mergeCell ref="A18:J18"/>
+    <mergeCell ref="A1:J2"/>
+    <mergeCell ref="A3:J3"/>
+    <mergeCell ref="G12:I12"/>
+    <mergeCell ref="G10:J10"/>
+    <mergeCell ref="H6:J6"/>
+    <mergeCell ref="H7:J7"/>
+    <mergeCell ref="A5:D5"/>
+    <mergeCell ref="A6:F6"/>
+    <mergeCell ref="H8:J8"/>
+    <mergeCell ref="H9:J9"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.25138888888888899" right="0.25138888888888899" top="0.39305555555555599" bottom="0.39305555555555599" header="0.29861111111111099" footer="0.29861111111111099"/>
